--- a/testData/sample_creds.xlsx
+++ b/testData/sample_creds.xlsx
@@ -1111,12 +1111,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>test12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>john123</t>
+          <t>newline12</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>test12</t>
+          <t>new</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>newline12</t>
+          <t>new1</t>
         </is>
       </c>
     </row>
